--- a/光伏配储项目/电价数据/2026/热水站.xlsx
+++ b/光伏配储项目/电价数据/2026/热水站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48291</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75562</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54091</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48404</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47521</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13436</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.0215</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20866</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02966</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15373</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13938</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.03542</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7340399999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12223</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19249</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66132</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86481</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47345</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19571</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.42225</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.28362</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98786</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28138</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.48778</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68244</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7326699999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08626</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95589</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89298</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8005399999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51471</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46484</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42761</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71733</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88963</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94271</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50275</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52516</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49171</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44733</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.15895</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.07974</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49255</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.11806</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12787</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.03779</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.00046</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.5219199999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03717</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.01703</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.68408</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.6216799999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78749</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.14495</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.22308</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.24603</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5934199999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.75486</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16146</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24962</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13155</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83788</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20528</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10619</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02235</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09042</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6513600000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9833200000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91406</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9577899999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78049</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88725</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7365700000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.7803</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72729</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7602100000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42985</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51325</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49327</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47788</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44172</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.19346</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78076</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43096</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42269</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50791</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47392</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28527</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6211100000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64564</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46614</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.54769</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48511</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61158</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48437</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6176699999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5705399999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55737</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.71692</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6017100000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55237</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45856</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51498</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.08515</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12897</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.25515</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17409</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15981</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12605</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62405</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50959</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46708</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47492</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48597</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5490499999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55806</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49464</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46921</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32135</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.09473000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07706</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09620999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.01193</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.16293</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.16225</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.04204</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.00993</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0184</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43323</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37227</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5757100000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.53442</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.54814</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43485</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.61811</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04477</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02764</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05132</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34782</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32369</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8692000000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54253</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43188</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45608</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.67055</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81792</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8843099999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.66973</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05282</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8748899999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51776</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9102100000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.84246</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59061</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48227</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5430900000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37238</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93663</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5306900000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55465</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.61713</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.22064</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08931</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20084</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5366599999999999</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47487</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46462</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46642</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7888500000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9493200000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48395</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20368</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.73089</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82285</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68202</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.8099400000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.60123</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47697</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52803</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46562</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44086</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45832</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51651</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.55261</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52452</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.51407</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63289</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.56659</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25176</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15738</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01706</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25909</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6551399999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.02674</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55775</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5129199999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37129</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.54864</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.51944</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5332899999999999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21447</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07137</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11572</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09090999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23018</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25627</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12756</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05265</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02902</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06422</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05631</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16131</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07490999999999999</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45703</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54726</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46589</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54638</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5350900000000001</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3916</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6833400000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44809</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.52443</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47482</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39542</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.64344</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1367</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67945</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51663</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46743</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46435</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43161</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17886</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.16765</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55824</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43271</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.11674</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43179</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58258</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48138</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72021</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.0603</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.72873</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42675</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.51881</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.42095</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44558</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42017</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43166</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46149</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44771</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.50896</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.47006</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36888</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.60119</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42233</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49242</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4353399999999999</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6752</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.0846</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.52497</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37473</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.10794</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23075</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.19776</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12584</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.24778</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15415</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24861</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.56741</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63847</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6567200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.65025</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8486900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.62337</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.20267</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.67362</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52462</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.46327</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.60776</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39027</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5932200000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73029</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.63446</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.90998</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48141</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45663</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47116</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46447</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.48968</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.56067</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.54852</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.73393</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62613</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54176</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.61514</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5378099999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46532</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54861</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64749</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.59204</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.22771</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.16603</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43121</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.53875</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6418700000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.70827</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.95427</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.18264</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.29983</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.93736</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.10809</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.92311</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.6998099999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.15136</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7887000000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6422599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69159</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.59324</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59016</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.57828</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.56998</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.69811</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.52042</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5454199999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45367</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.57811</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45214</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43681</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.62297</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01973</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.10446</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.03238000000000001</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44582</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49201</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45477</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52432</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48621</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.46779</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6269199999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.6277699999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.5969099999999999</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.46956</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.6048600000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.5659099999999999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.46337</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55062</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.46987</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.5488099999999999</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.56525</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.4959</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.5651799999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.20856</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21078</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07119</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18198</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21389</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44826</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42629</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.49105</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.46589</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42664</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51156</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48403</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.51376</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.51503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.5081100000000001</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.52603</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03386</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00095</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15157</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01489</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02948</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03747</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01497</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03558</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20569</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.51878</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41045</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.19047</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.0208</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49431</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8797999999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5271399999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.51073</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.47222</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48533</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.63983</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.66234</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.65379</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.59835</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6555299999999999</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.62336</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.60578</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.63074</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6727300000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.5963999999999999</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52291</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.51214</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.41264</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91124</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87299</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.03367</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.02778</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.006160000000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.00388</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04198</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00842</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.04801</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.15842</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.1166</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00077</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.14429</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.04978</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15166</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86325</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86563</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96245</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.14677</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.14763</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.14097</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.42281</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60629</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.89608</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.47683</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.84158</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51919</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.62546</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.52071</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.52113</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.48796</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.53271</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6685099999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46097</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.6236699999999999</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.50907</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.61766</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6745099999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52524</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.16787</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.19155</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.16179</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.63125</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.24963</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9172899999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.61464</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.54899</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.53975</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42716</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40401</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.51567</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48558</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.47955</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.54983</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8608300000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.0152</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8412200000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.78054</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6007100000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.00649</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83217</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58216</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55748</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65761</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8169099999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.57374</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.92645</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.8107000000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6132000000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.61595</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43873</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46701</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40335</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43908</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5128200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66637</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.69859</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.78546</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54696</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.77952</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48146</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6026699999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.94872</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5127200000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.52883</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.01813</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40762</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40403</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17769</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17462</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18356</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01262</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05725</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11141</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00376</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18355</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20852</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54628</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45926</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.5202599999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41971</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.26306</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.20868</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23174</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.12329</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41968</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38937</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48343</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17687</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02083</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03312</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02351</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.00066</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.01514</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.01796</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13783</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.02222</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.06856</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18212</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.006030000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23545</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.17449</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.01976</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51059</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40871</v>
       </c>
     </row>
   </sheetData>
